--- a/Resumen_Ejecutivo_Cobertura_IPERC.xlsx
+++ b/Resumen_Ejecutivo_Cobertura_IPERC.xlsx
@@ -617,29 +617,29 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Personal administrativo  ·  Plantaciones de Balsa Plantabal S.A. / 3A Core Materials  ·  Head count de octubre de 2026  ·  Corte al 14/10/2026</t>
+          <t>Personal administrativo  ·  Plantaciones de Balsa Plantabal S.A. / 3A Core Materials  ·  Head count de octubre de 2026  ·  Corte al 22/10/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -649,13 +649,13 @@
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>de los cargos con matriz
-58 de 71 cargos</t>
+59 de 71 cargos</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>del personal cubierto
-80 de 99 personas</t>
+87 de 99 personas</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -860,22 +860,22 @@
         <v>22</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>36</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -992,22 +992,22 @@
         <v>71</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="20" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18" s="19" t="n">
         <v>99</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I18" s="18" t="inlineStr"/>
     </row>
@@ -1060,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1113,22 +1113,22 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Operaciones</t>
+          <t>ADM-L&amp;RH</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>SUPERVISOR DE PRODUCCIÓN</t>
+          <t>COORDINADOR DE SEGURIDAD FISICA</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -1139,22 +1139,22 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>ADM-L&amp;RH</t>
+          <t>Gerencia</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>COORDINADOR DE SEGURIDAD FISICA</t>
+          <t>CHOFER</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>CHOFER</t>
+          <t>GERENTE GENERAL</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -1191,22 +1191,22 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Gerencia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>GERENTE GENERAL</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -1217,22 +1217,22 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>IT&amp;FIN</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>ANALISTA DE IMPUESTOS</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
@@ -1248,17 +1248,17 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>ANALISTA DE IMPUESTOS</t>
+          <t>DIRECTOR FINANCIERO</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -1274,17 +1274,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>DIRECTOR FINANCIERO</t>
+          <t>GERENTE FINANCIERO</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>GERENTE FINANCIERO</t>
+          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>JEFE  DE DESARROLLO DE APLICACIONES</t>
+          <t>JUNIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>JUNIOR BUSINESS CONTROLLER</t>
+          <t>SENIOR BUSINESS CONTROLLER</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1373,22 +1373,22 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>IT&amp;FIN</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>SENIOR BUSINESS CONTROLLER</t>
+          <t>APRENDIZ</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -1404,45 +1404,19 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>APRENDIZ</t>
+          <t>JEFE DE BODEGA</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Elaborar matriz IPERC para el puesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Operaciones</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>JEFE DE BODEGA</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Elaborar matriz IPERC para el puesto</t>
         </is>
@@ -1452,7 +1426,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D16">
+  <conditionalFormatting sqref="D4:D15">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
